--- a/daily_matches/job_matches_2026-07-15.xlsx
+++ b/daily_matches/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Artificial Intelligence</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, XGBoost, spaCy, S3, EC2</t>
+          <t>RAG, S3, Glue, CI/CD, Terraform, PySpark, Kafka, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Scientist (Machine Learning &amp; Generative AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, EC2, Glue, Athena</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221a044944e1b41d</t>
+          <t>https://www.indeed.com/viewjob?jk=eceb0995fb9afae0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, S3, BigQuery, Kinesis, MLflow, Kubernetes</t>
+          <t>Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7899e9d8663f480c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, S3, BigQuery, Kinesis, MLflow, Kubernetes</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, MLflow, Databricks, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=c51b8eec978a716e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, BigQuery, Kinesis, CI/CD, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, MLflow, Databricks, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=173a0cc589c330e2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GenAI Data Scientist, Commercial, Supply Chain &amp; Trading</t>
+          <t>Sr. Software Engineer, Data Platform, Factory Software</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git</t>
+          <t>RAG, Kinesis, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace440deb58cf019</t>
+          <t>https://www.indeed.com/viewjob?jk=3e43408e68474559</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Data Analytics Engineer</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Power BI</t>
+          <t>RAG, S3, Redshift, MLflow, CI/CD, Terraform, Git, Snowflake, Redshift, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=742fc2b4eb545651</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solution Architect - Agentic AI &amp; Data</t>
+          <t>Sr. AI Engineer, Application Security</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e62edbf8c4a89</t>
+          <t>https://www.indeed.com/viewjob?jk=6df63f19d4949e5e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Java Python AWS Developer</t>
+          <t>Software Development Engineer in Test 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Choice Hotels</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, EC2, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826d55cde3389181</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a54c834d9a7a50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, CI/CD, Git, Kafka, SQL, R</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb5b525d0b72c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa32335e4b830851</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer â€“ Golang, System Design, Kubernetes Platform Development &amp; AI Automation</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a814808eb4f077b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae860adcfaabeaf7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Full Stack Centennial, CO - Hybrid • Hybrid</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eeddd2f27c1bce2</t>
+          <t>https://www.indeed.com/viewjob?jk=c9964962eadf4e57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Full Stack</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,137 +916,137 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8f0557e538fbdc</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f11231c888f3b3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
+          <t>https://www.indeed.com/viewjob?jk=c8090bc5661d1649</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
+          <t>https://www.indeed.com/viewjob?jk=2f294ad9fed06a69</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II, Search and Recommendations</t>
+          <t>Technology Solutions Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>CEC Facilities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,322 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebba4b09c33f10f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Search &amp; Recommendations</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Wayfair</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce142e0b825940e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Enverus</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Terraform, Kafka, MongoDB, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68da7bc0031a87a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Near-Miss Management</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72efd898a32a6b4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AI Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Nextiva</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fe7793d86ea6ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Diagnostics Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Data Lake, BigQuery, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cb3258f583fb56</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BillGO, Inc.</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fort Collins, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, Snowflake, Tableau, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4545e053edf36479</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Scientist, Bioinformatics / Computational Biology</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>AstraZeneca</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f697746f920094</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineering MTS</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Tableau, Python, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=786816c6d1a61503</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Elite Talent Hub</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81a82b29106fd152</t>
+          <t>https://www.indeed.com/viewjob?jk=22869b38f8083164</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-15.xlsx
+++ b/daily_matches/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Artificial Intelligence Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, CI/CD, Terraform, PySpark, Kafka, PostgreSQL, MySQL, NoSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, XGBoost, spaCy, S3, EC2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
+          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (Machine Learning &amp; Generative AI)</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,77 +521,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, Docker, CI/CD, Git</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eceb0995fb9afae0</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Performance Engineer, Information technology</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Hadoop, Python, R</t>
+          <t>Generative AI, RAG, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7899e9d8663f480c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, MLflow, Databricks, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, MLflow, Kubernetes, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51b8eec978a716e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8466d78980a1ab</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, MLflow, Databricks, Python</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173a0cc589c330e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Platform, Factory Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+          <t>RAG, Copilot, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e43408e68474559</t>
+          <t>https://www.indeed.com/viewjob?jk=0afd7c69b484eecb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>DevOps Engineer IV 4P/763</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, MLflow, CI/CD, Terraform, Git, Snowflake, Redshift, R</t>
+          <t>LangChain, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,357 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7bb2eca4c76d5e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer, Application Security</t>
+          <t>Senior Advanced Solutions Architect - Data Platforms</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, R</t>
+          <t>Generative AI, RAG, Databricks, Kafka, NoSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df63f19d4949e5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test 2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Choice Hotels</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, EC2, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a54c834d9a7a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa32335e4b830851</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae860adcfaabeaf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9964962eadf4e57</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f11231c888f3b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8090bc5661d1649</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f294ad9fed06a69</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>AutoSavvy</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Woods Cross, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Technology Solutions Analyst</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CEC Facilities</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22869b38f8083164</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce7f6129b1514c8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-15.xlsx
+++ b/daily_matches/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Senior Data Scientist</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, XGBoost, spaCy, S3, EC2</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
+          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Performance Engineer, Information technology</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Applied Machine Learning Engineer</t>
+          <t>Software Engineer I - Credit Karma</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, MLflow, Kubernetes, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8466d78980a1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7b8b53f5d1b6d6d1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Senior Python Software Engineer – SQL &amp; Generative AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,69 +626,69 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=2acea39a6fa0e17f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Decision Six</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0afd7c69b484eecb</t>
+          <t>https://www.indeed.com/viewjob?jk=36b78ad310bd4185</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV 4P/763</t>
+          <t>GEN AI PRODUCT OWNER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Cortex, Snowflake, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7bb2eca4c76d5e</t>
+          <t>https://www.indeed.com/viewjob?jk=278eb8ec2a145bbd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Advanced Solutions Architect - Data Platforms</t>
+          <t>Data Scientist (Entry Level)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Parahunt Global Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,122 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Databricks, Kafka, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce7f6129b1514c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0d57130629e93549</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Systems Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=691f47db921bf4ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c205267eef2abf6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb7d3b2b58f1f36a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-15.xlsx
+++ b/daily_matches/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>S3, EC2, Docker, Git, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
+          <t>Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, Data Lake, Git, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f8ebfce6a7fa7c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer I - Credit Karma</t>
+          <t>Senior Support Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8b53f5d1b6d6d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5f65d74d6617ff09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer – SQL &amp; Generative AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, Git, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, Quicksight, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acea39a6fa0e17f</t>
+          <t>https://www.indeed.com/viewjob?jk=9292628350960543</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Internal Applications Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Decision Six</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Optimization</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Git, Snowflake, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36b78ad310bd4185</t>
+          <t>https://www.indeed.com/viewjob?jk=525bbc16d2fc6928</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GEN AI PRODUCT OWNER</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Cortex, Snowflake, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278eb8ec2a145bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=88a0a8a86f81e0fb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist (Entry Level)</t>
+          <t>Software Development Engineer II - Backend-Focused Full-Stack</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Parahunt Global Solutions</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d57130629e93549</t>
+          <t>https://www.indeed.com/viewjob?jk=20cb7752c490da7d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Systems Reliability Engineer</t>
+          <t>Software Support Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691f47db921bf4ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MLflow, Snowflake, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c205267eef2abf6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MLflow, Snowflake, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb7d3b2b58f1f36a</t>
+          <t>https://www.indeed.com/viewjob?jk=03544d883ac9f7c8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-15.xlsx
+++ b/daily_matches/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Senior Specialist - Data Sciences</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Git, MySQL, MongoDB, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Cortex, TensorFlow, PyTorch, XGBoost, Azure ML</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=e4fa4d66fb7f1c69</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Senior Machine Learning Engineer, Recommendations</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>Arena Club</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, EC2, MLflow, PySpark, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=98a6730ae6024507</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Lightspeed DMS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f8ebfce6a7fa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e18e17ef8469033</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Support Software Engineer</t>
+          <t>GenAI - EAI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f65d74d6617ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d388d276618c8a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, Quicksight, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, FastAPI, Docker, CI/CD, Git, Snowflake, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9292628350960543</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Internal Applications Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Git, Snowflake, Python, R, Java</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=525bbc16d2fc6928</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Developer - Full Stack - Java - Hybrid - 4 days - Arlington, Virginia</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88a0a8a86f81e0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a313e1e7c7ad78</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Backend-Focused Full-Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, R, Java, Scala, Optimization</t>
+          <t>RAG, Redshift, Synapse, CI/CD, Git, Snowflake, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,427 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cb7752c490da7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Support Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, Kubernetes, AKS, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdf53e6f18a64923</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Monarchouse</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fullerton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bb2087d6d14e976</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Jenkins, Terraform, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst I - REMOTE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Net Health</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cortex, Redshift, Git, Snowflake, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Transportation Data Scientist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Citian</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03544d883ac9f7c8</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, spaCy, NLTK, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f1a0f6d924ffe4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcad7d47362622d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Malvern, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e942d6be48a7025a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=278044da08dd9782</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RedSail Technologies</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spartanburg, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=827904d10b8d5893</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d6aa1370ac3591f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe03ea12bd40fb49</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Intern</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Metz Lewis Brodman Must O'Keefe</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, FastAPI, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc547fc57bc2fc2c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-15.xlsx
+++ b/daily_matches/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Sciences</t>
+          <t>Sr. Software Engineer - AI Platforms and Automation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Cortex, TensorFlow, PyTorch, XGBoost, Azure ML</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, S3, Glue, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4fa4d66fb7f1c69</t>
+          <t>https://www.indeed.com/viewjob?jk=60174baa1f0aad14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Recommendations</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arena Club</t>
+          <t>Axiomatic AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, EC2, MLflow, PySpark, Python</t>
+          <t>RAG, AWS SageMaker, Azure ML, FastAPI, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a6730ae6024507</t>
+          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lightspeed DMS</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, MLflow, CI/CD, Databricks, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e18e17ef8469033</t>
+          <t>https://www.indeed.com/viewjob?jk=6e899285a709ae99</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GenAI - EAI Engineer</t>
+          <t>Software Engineer - Finance Tech</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d388d276618c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=921fbb9dc16ea6e9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Data Platform Engineer (Data 360)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, CI/CD, Git, Snowflake, Databricks, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, Data Lake, Kinesis, Snowflake, Databricks, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior AI/ML Developer – Financial Services</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Astre Consulting Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Kafka, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb90c8f262b0ef8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Software Developer - Full Stack - Java - Hybrid - 4 days - Arlington, Virginia</t>
+          <t>Technical Architect - Enterprise Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Copilot, Prompt Engineering, Data Lake, CI/CD, Git, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a313e1e7c7ad78</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Synapse, CI/CD, Git, Snowflake, Redshift, Tableau, Python, SQL</t>
+          <t>AI Engineer, RAG, MLflow, CI/CD, Terraform, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Kubernetes, AKS, Git, BigQuery, Python, SQL, R</t>
+          <t>RAG, Synapse, Data Lake, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf53e6f18a64923</t>
+          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Monarchouse</t>
+          <t>Data Surge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fullerton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Databricks, MySQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb2087d6d14e976</t>
+          <t>https://www.indeed.com/viewjob?jk=9fcc7aeb481b42ce</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, CI/CD, Jenkins, Terraform, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cortex, Redshift, Git, Snowflake, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f78f10325d0dd187</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Citian</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, spaCy, NLTK, Snowflake, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1a0f6d924ffe4c</t>
+          <t>https://www.indeed.com/viewjob?jk=86b4d8d2f561c1b2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Security Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Sound Physicians</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Git, Python, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcad7d47362622d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0c296dde0ffe66ce</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Full Stack | AI Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>CI/CD, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e942d6be48a7025a</t>
+          <t>https://www.indeed.com/viewjob?jk=80c4b497c4690c21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>AI Arhitect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278044da08dd9782</t>
+          <t>https://www.indeed.com/viewjob?jk=05cc824ab401d205</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer - Customer Success</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RedSail Technologies</t>
+          <t>Feedzai</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spartanburg, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kafka, Cassandra, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=827904d10b8d5893</t>
+          <t>https://www.indeed.com/viewjob?jk=60104c7a8b6f0c7e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Analytics and Research Analyst</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>VINMAR INTERNATIONAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, FastAPI, Docker, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6aa1370ac3591f</t>
+          <t>https://www.indeed.com/viewjob?jk=43aa1a5e37a0ff4a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Customer Architect (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Harness</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,42 +1126,322 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe03ea12bd40fb49</t>
+          <t>https://www.indeed.com/viewjob?jk=62ac2172c8a9bb70</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Software Engineer III - IBM i (AS/400) Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Metz Lewis Brodman Must O'Keefe</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1678c1edf6d1059f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist - R&amp;D (AI/ML)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Vermeer Corporation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ames, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, MLflow, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c919d76ae911e04c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quarterhill</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, FastAPI, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc547fc57bc2fc2c</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, OpenCV, MLflow, Docker, Kubernetes, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07023bd2f3c9635</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89fa6dbfafd3c47c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Engineer - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Primoris Services Corporation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software QA Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HME</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15209136e4201346</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>.Net Developer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Troy Web Consulting</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cohoes, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e02a3fc063414e07</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>.Net Developer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Troy Web Consulting</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cohoes, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06c18030428d42a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>.Net Developer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Troy Web Consulting</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cohoes, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e720a2b31e31e16</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-15.xlsx
+++ b/daily_matches/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Platforms and Automation</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>45.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, S3, Glue, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, FAISS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60174baa1f0aad14</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9e10d0ccdb5375</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Specialty AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, Azure ML, FastAPI, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
+          <t>https://www.indeed.com/viewjob?jk=fae61332bbf7f3a6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Specialty AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, MLflow, CI/CD, Databricks, MongoDB</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e899285a709ae99</t>
+          <t>https://www.indeed.com/viewjob?jk=364a52b2f314bb47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer - Finance Tech</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Prompt Engineering, Azure ML, MLflow, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=921fbb9dc16ea6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Data 360)</t>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, Data Lake, Kinesis, Snowflake, Databricks, Kafka, Tableau</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer – Financial Services</t>
+          <t>Sr AI Engineer (RAG Specialist with Strong Python Skills)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Astre Consulting Services</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Kafka, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb90c8f262b0ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=90789e33ce4eaf0c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>Sr AI Engineer (RAG Specialist with Strong Python Skills)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Data Lake, CI/CD, Git, PySpark, Power BI, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=24eccf7f8d847917</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, MLflow, CI/CD, Terraform, Git, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Databricks, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+          <t>Generative AI, S3, Glue, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Expert Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Data Surge</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Databricks, MySQL, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, TensorFlow, Git, Hadoop, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fcc7aeb481b42ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9492d4954650eb7f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, Prompt Engineering, Cortex, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb0f86df0020154</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Machine Learning AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
+          <t>AI Engineer, RAG, LLaMA, Copilot, Mistral, Docker, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78f10325d0dd187</t>
+          <t>https://www.indeed.com/viewjob?jk=de558210ca4d4736</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86b4d8d2f561c1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=f24000cfeb877020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Application Security Analyst</t>
+          <t>Software Engineer - Drive OS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sound Physicians</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c296dde0ffe66ce</t>
+          <t>https://www.indeed.com/viewjob?jk=381e9446e2fecbad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack | AI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CI/CD, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Glue, Athena, Apache Airflow, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c4b497c4690c21</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Arhitect</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cc824ab401d205</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - Customer Success</t>
+          <t>GenAI Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Feedzai</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kafka, Cassandra, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60104c7a8b6f0c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0e66289e851076</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VINMAR INTERNATIONAL</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Kinesis, Terraform, Git, Kafka, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43aa1a5e37a0ff4a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Customer Architect (Forward Deployed Engineer)</t>
+          <t>GCP Solutions Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Harness</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, BigQuery, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ac2172c8a9bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - IBM i (AS/400) Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, BigQuery, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1678c1edf6d1059f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist - R&amp;D (AI/ML)</t>
+          <t>.NET Architect (AWS &amp; GenAI)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vermeer Corporation</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ames, IA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, MLflow, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Kubernetes, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c919d76ae911e04c</t>
+          <t>https://www.indeed.com/viewjob?jk=11203a6462da16c6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, OpenCV, MLflow, Docker, Kubernetes, R, Scala, Optimization</t>
+          <t>RAG, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07023bd2f3c9635</t>
+          <t>https://www.indeed.com/viewjob?jk=e97c6b01aba989af</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Oracle Fusion Techno-Functional Developer- Remote, US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Data Lake, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fa6dbfafd3c47c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4bf2dbbd42dbbf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>RPA Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, TensorFlow, PyTorch, Git, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=80556701df25b483</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software QA Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HME</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15209136e4201346</t>
+          <t>https://www.indeed.com/viewjob?jk=4926058441ec091f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>.Net Developer</t>
+          <t>Agentic AI Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Troy Web Consulting</t>
+          <t>DataRobot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cohoes, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
+          <t>Generative AI, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Python, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,77 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02a3fc063414e07</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>.Net Developer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Troy Web Consulting</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Cohoes, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06c18030428d42a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>.Net Developer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Troy Web Consulting</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Cohoes, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e720a2b31e31e16</t>
+          <t>https://www.indeed.com/viewjob?jk=8b545d9cb441528f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-15.xlsx
+++ b/daily_matches/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45.6</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, FAISS</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9e10d0ccdb5375</t>
+          <t>https://www.indeed.com/viewjob?jk=70b73d6d3922b6ec</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Specialty AI Engineer</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae61332bbf7f3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=bd35c029ba02435f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Specialty AI Engineer</t>
+          <t>Senior Software Engineer - Backend (Go)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364a52b2f314bb47</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1d1cdd35cbd5c1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer, New College Grad - 2026, Foster City</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Prompt Engineering, Azure ML, MLflow, Git, Snowflake, Databricks</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=6fde336d8caba0b6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>Senior Software Engineer - Backend (Go)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0a10a9635bdeb8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr AI Engineer (RAG Specialist with Strong Python Skills)</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Git, BigQuery, Kafka, Tableau, Power BI, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90789e33ce4eaf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr AI Engineer (RAG Specialist with Strong Python Skills)</t>
+          <t>Software Engineer II - Commerce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24eccf7f8d847917</t>
+          <t>https://www.indeed.com/viewjob?jk=5d338f665f2fb51d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Databricks, NoSQL, Python</t>
+          <t>RAG, S3, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>Parametrix, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Glue, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
+          <t>https://www.indeed.com/viewjob?jk=229816501e436973</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Expert Data Scientist</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Parametrix, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, TensorFlow, Git, Hadoop, NoSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9492d4954650eb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b3c37ec53541c7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>Parametrix, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, Prompt Engineering, Cortex, Snowflake, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb0f86df0020154</t>
+          <t>https://www.indeed.com/viewjob?jk=0f8f8a8199115e74</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Machine Learning AI Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Parametrix, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Copilot, Mistral, Docker, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de558210ca4d4736</t>
+          <t>https://www.indeed.com/viewjob?jk=4b4b25ebf0fa3d04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>Parametrix, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f24000cfeb877020</t>
+          <t>https://www.indeed.com/viewjob?jk=7579943f8be77f9d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer - Drive OS</t>
+          <t>Senior Software Engineer, Sensors &amp; Embodied Intelligence</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381e9446e2fecbad</t>
+          <t>https://www.indeed.com/viewjob?jk=b0af8128cc288b2e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Apache Airflow, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Oracle Fusion Techno-Functional Developer- Remote, US</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Data Lake, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=43ecdecd1b377705</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GenAI Analyst</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Indica Labs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Python, R</t>
+          <t>S3, EC2, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0e66289e851076</t>
+          <t>https://www.indeed.com/viewjob?jk=b038ea70da05814c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Terraform, Git, Kafka, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Solutions Architect</t>
+          <t>Associate Data and Cost Modeling Analyst - Government Estimating</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>Hazelwood, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, BigQuery, Hadoop, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Databricks, PySpark, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,252 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>GCP Data Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Core BTS</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Menasha, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, BigQuery, Hadoop, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>.NET Architect (AWS &amp; GenAI)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, Kubernetes, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11203a6462da16c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Cyber Security Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e97c6b01aba989af</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Oracle Fusion Techno-Functional Developer- Remote, US</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Data Lake, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4bf2dbbd42dbbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RPA Developer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Echo Global Logistics</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, Git, Matplotlib, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80556701df25b483</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Alarm.com</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4926058441ec091f</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Agentic AI Intern</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>DataRobot</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b545d9cb441528f</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f177e568ac3c1</t>
         </is>
       </c>
     </row>
